--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="45">
   <si>
     <t>ARTID</t>
   </si>
@@ -83,6 +83,9 @@
     <t>REASON_DETAIL</t>
   </si>
   <si>
+    <t>OTHEREXPEND</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
     <t>25/09/2025</t>
   </si>
   <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
     <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
     <t>ΑΛΠ 165</t>
   </si>
   <si>
+    <t>TΔA 60939</t>
+  </si>
+  <si>
     <t>64-99-98-0087</t>
   </si>
   <si>
@@ -137,16 +146,10 @@
     <t>ΕΠΩΝΥΜΙΑ</t>
   </si>
   <si>
-    <t>000000000</t>
-  </si>
-  <si>
     <t>800916954</t>
   </si>
   <si>
     <t>094439854</t>
-  </si>
-  <si>
-    <t>ΠΡΟΜΗΘΕΥΤΕΣ ΔΑΠΑΝΩΝ</t>
   </si>
 </sst>
 </file>
@@ -511,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -527,9 +530,10 @@
     <col min="18" max="20" width="14.7109375" style="3" customWidth="1"/>
     <col min="21" max="21" width="18.7109375" customWidth="1"/>
     <col min="22" max="22" width="40.7109375" customWidth="1"/>
+    <col min="23" max="23" width="10.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -596,13 +600,16 @@
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -614,13 +621,13 @@
         <v>20254</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3">
         <v>13.83</v>
@@ -632,7 +639,7 @@
         <v>3.32</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -650,18 +657,21 @@
         <v>17.15</v>
       </c>
       <c r="U2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
+        <v>28</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -673,13 +683,13 @@
         <v>20254</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3">
         <v>13.83</v>
@@ -691,7 +701,7 @@
         <v>3.32</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -709,18 +719,21 @@
         <v>17.15</v>
       </c>
       <c r="U3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>28</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -732,13 +745,13 @@
         <v>14460</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3">
         <v>104.99</v>
@@ -750,7 +763,7 @@
         <v>23.91</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
@@ -768,18 +781,21 @@
         <v>121.31</v>
       </c>
       <c r="U4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+        <v>29</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -791,13 +807,13 @@
         <v>14460</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3">
         <v>104.99</v>
@@ -809,7 +825,7 @@
         <v>23.91</v>
       </c>
       <c r="N5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -827,18 +843,21 @@
         <v>7.59</v>
       </c>
       <c r="U5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+        <v>29</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -850,13 +869,13 @@
         <v>14460</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3">
         <v>104.99</v>
@@ -868,7 +887,7 @@
         <v>23.91</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -886,18 +905,21 @@
         <v>128.9</v>
       </c>
       <c r="U6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+        <v>29</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -906,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>170</v>
+        <v>142076</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7" s="3">
         <v>9.4</v>
@@ -927,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -945,18 +967,21 @@
         <v>9.4</v>
       </c>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+        <v>30</v>
+      </c>
+      <c r="W7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" s="1">
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -965,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>170</v>
+        <v>142076</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3">
         <v>9.4</v>
@@ -986,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1004,10 +1029,137 @@
         <v>9.4</v>
       </c>
       <c r="U8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V8" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="W8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>14460</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-33.06</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>-7.93</v>
+      </c>
+      <c r="N9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>-33.06</v>
+      </c>
+      <c r="S9" s="3">
+        <v>-7.93</v>
+      </c>
+      <c r="T9" s="3">
+        <v>-40.99</v>
+      </c>
+      <c r="U9" t="s">
+        <v>34</v>
+      </c>
+      <c r="V9" t="s">
+        <v>29</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>14460</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-33.06</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>-7.93</v>
+      </c>
+      <c r="N10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3">
+        <v>-33.06</v>
+      </c>
+      <c r="S10" s="3">
+        <v>-7.93</v>
+      </c>
+      <c r="T10" s="3">
+        <v>-40.99</v>
+      </c>
+      <c r="U10" t="s">
+        <v>34</v>
+      </c>
+      <c r="V10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1027,46 +1179,43 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>20254</v>
+        <v>142076</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
   <si>
     <t>ARTID</t>
   </si>
@@ -122,19 +122,28 @@
     <t>TΔA 60939</t>
   </si>
   <si>
-    <t>64-99-98-0087</t>
+    <t>64-98-99-0087</t>
+  </si>
+  <si>
+    <t>63-98-08-0000</t>
   </si>
   <si>
     <t>50-00-00-0000</t>
   </si>
   <si>
-    <t>20-00-10-0087</t>
-  </si>
-  <si>
-    <t>64-00-00-0025</t>
-  </si>
-  <si>
-    <t>64-00-00-0000</t>
+    <t>20-02-00-0024</t>
+  </si>
+  <si>
+    <t>54-02-02-2024</t>
+  </si>
+  <si>
+    <t>64-12-00-0006</t>
+  </si>
+  <si>
+    <t>54-02-02-6006</t>
+  </si>
+  <si>
+    <t>64-12-00-0000</t>
   </si>
   <si>
     <t>Α/Α</t>
@@ -146,10 +155,16 @@
     <t>ΕΠΩΝΥΜΙΑ</t>
   </si>
   <si>
+    <t>000000000</t>
+  </si>
+  <si>
     <t>800916954</t>
   </si>
   <si>
     <t>094439854</t>
+  </si>
+  <si>
+    <t>ΠΡΟΜΗΘΕΥΤΕΣ ΔΑΠΑΝΩΝ</t>
   </si>
 </sst>
 </file>
@@ -514,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -651,10 +666,10 @@
         <v>13.83</v>
       </c>
       <c r="S2" s="3">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
-        <v>17.15</v>
+        <v>13.83</v>
       </c>
       <c r="U2" t="s">
         <v>31</v>
@@ -707,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="Q3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="3">
-        <v>13.83</v>
+        <v>3.32</v>
       </c>
       <c r="S3" s="3">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3">
         <v>3.32</v>
-      </c>
-      <c r="T3" s="3">
-        <v>17.15</v>
       </c>
       <c r="U3" t="s">
         <v>31</v>
@@ -730,7 +745,7 @@
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>23</v>
@@ -742,25 +757,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3">
-        <v>104.99</v>
+        <v>13.83</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
       </c>
       <c r="K4" s="3">
-        <v>23.91</v>
+        <v>3.32</v>
       </c>
       <c r="N4" t="s">
         <v>37</v>
@@ -769,22 +784,22 @@
         <v>0</v>
       </c>
       <c r="Q4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="3">
-        <v>97.83</v>
+        <v>13.83</v>
       </c>
       <c r="S4" s="3">
-        <v>23.48</v>
+        <v>3.32</v>
       </c>
       <c r="T4" s="3">
-        <v>121.31</v>
+        <v>17.15</v>
       </c>
       <c r="U4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
@@ -834,13 +849,13 @@
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <v>7.16</v>
+        <v>97.83</v>
       </c>
       <c r="S5" s="3">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>7.59</v>
+        <v>97.83</v>
       </c>
       <c r="U5" t="s">
         <v>32</v>
@@ -887,22 +902,22 @@
         <v>23.91</v>
       </c>
       <c r="N6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3">
-        <v>104.99</v>
+        <v>23.48</v>
       </c>
       <c r="S6" s="3">
-        <v>23.91</v>
+        <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>128.9</v>
+        <v>23.48</v>
       </c>
       <c r="U6" t="s">
         <v>32</v>
@@ -916,7 +931,7 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>23</v>
@@ -928,28 +943,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>142076</v>
+        <v>14460</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3">
-        <v>9.4</v>
+        <v>104.99</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -958,27 +973,27 @@
         <v>0</v>
       </c>
       <c r="R7" s="3">
-        <v>9.4</v>
+        <v>7.16</v>
       </c>
       <c r="S7" s="3">
         <v>0</v>
       </c>
       <c r="T7" s="3">
-        <v>9.4</v>
+        <v>7.16</v>
       </c>
       <c r="U7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>23</v>
@@ -990,57 +1005,57 @@
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>142076</v>
+        <v>14460</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3">
-        <v>9.4</v>
+        <v>104.99</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="N8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
       </c>
       <c r="Q8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>9.4</v>
+        <v>0.43</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>9.4</v>
+        <v>0.43</v>
       </c>
       <c r="U8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>23</v>
@@ -1055,22 +1070,22 @@
         <v>14460</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
         <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3">
-        <v>-33.06</v>
+        <v>104.99</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>-7.93</v>
+        <v>23.91</v>
       </c>
       <c r="N9" t="s">
         <v>37</v>
@@ -1079,19 +1094,19 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="3">
-        <v>-33.06</v>
+        <v>104.99</v>
       </c>
       <c r="S9" s="3">
-        <v>-7.93</v>
+        <v>23.91</v>
       </c>
       <c r="T9" s="3">
-        <v>-40.99</v>
+        <v>128.9</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V9" t="s">
         <v>29</v>
@@ -1102,7 +1117,7 @@
     </row>
     <row r="10" spans="1:23">
       <c r="A10" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -1114,51 +1129,299 @@
         <v>0</v>
       </c>
       <c r="E10" s="1">
+        <v>170</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>42</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="U10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V10" t="s">
+        <v>30</v>
+      </c>
+      <c r="W10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>170</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="U11" t="s">
+        <v>33</v>
+      </c>
+      <c r="V11" t="s">
+        <v>30</v>
+      </c>
+      <c r="W11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="1">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
         <v>14460</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I12" s="3">
         <v>-33.06</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>-7.93</v>
       </c>
-      <c r="N10" t="s">
-        <v>36</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="N12" t="s">
+        <v>38</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
         <v>-33.06</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>-33.06</v>
+      </c>
+      <c r="U12" t="s">
+        <v>34</v>
+      </c>
+      <c r="V12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="1">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>14460</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="3">
+        <v>-33.06</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
         <v>-7.93</v>
       </c>
-      <c r="T10" s="3">
+      <c r="N13" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>-7.93</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>-7.93</v>
+      </c>
+      <c r="U13" t="s">
+        <v>34</v>
+      </c>
+      <c r="V13" t="s">
+        <v>29</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="1">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>14460</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-33.06</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-7.93</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>1</v>
+      </c>
+      <c r="R14" s="3">
+        <v>-33.06</v>
+      </c>
+      <c r="S14" s="3">
+        <v>-7.93</v>
+      </c>
+      <c r="T14" s="3">
         <v>-40.99</v>
       </c>
-      <c r="U10" t="s">
+      <c r="U14" t="s">
         <v>34</v>
       </c>
-      <c r="V10" t="s">
-        <v>29</v>
-      </c>
-      <c r="W10" s="1">
+      <c r="V14" t="s">
+        <v>29</v>
+      </c>
+      <c r="W14" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1179,43 +1442,46 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>14460</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>20254</v>
+        <v>14460</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>142076</v>
+        <v>20254</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
   <si>
     <t>ARTID</t>
   </si>
@@ -92,34 +92,25 @@
     <t>03/10/2025</t>
   </si>
   <si>
-    <t>11/11/2025</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>10/11/2025</t>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>12/11/2025</t>
   </si>
   <si>
     <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
   </si>
   <si>
-    <t>ΑΦΟΙ ΛΑΓΟΥ ΧΡΩΜΑΤΑ ΙΚΕ</t>
-  </si>
-  <si>
-    <t>094386010</t>
+    <t>801466788</t>
   </si>
   <si>
     <t>12Μ0ΤΔΑ 10768</t>
   </si>
   <si>
-    <t>TΔA 60984</t>
-  </si>
-  <si>
-    <t>ΑΛΠ 165</t>
-  </si>
-  <si>
-    <t>TΔA 60939</t>
+    <t>ΑΛΠ 61010</t>
+  </si>
+  <si>
+    <t>11Μ0ΤΔΑ 9480</t>
   </si>
   <si>
     <t>64-98-99-0087</t>
@@ -131,21 +122,15 @@
     <t>50-00-00-0000</t>
   </si>
   <si>
+    <t>64-12-00-0000</t>
+  </si>
+  <si>
     <t>20-02-00-0024</t>
   </si>
   <si>
     <t>54-02-02-2024</t>
   </si>
   <si>
-    <t>64-12-00-0006</t>
-  </si>
-  <si>
-    <t>54-02-02-6006</t>
-  </si>
-  <si>
-    <t>64-12-00-0000</t>
-  </si>
-  <si>
     <t>Α/Α</t>
   </si>
   <si>
@@ -156,9 +141,6 @@
   </si>
   <si>
     <t>000000000</t>
-  </si>
-  <si>
-    <t>800916954</t>
   </si>
   <si>
     <t>094439854</t>
@@ -529,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -639,10 +621,10 @@
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I2" s="3">
         <v>13.83</v>
@@ -654,7 +636,7 @@
         <v>3.32</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -672,10 +654,10 @@
         <v>13.83</v>
       </c>
       <c r="U2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="V2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W2" s="1">
         <v>0</v>
@@ -701,10 +683,10 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3">
         <v>13.83</v>
@@ -716,7 +698,7 @@
         <v>3.32</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -734,10 +716,10 @@
         <v>3.32</v>
       </c>
       <c r="U3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -763,10 +745,10 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3">
         <v>13.83</v>
@@ -778,7 +760,7 @@
         <v>3.32</v>
       </c>
       <c r="N4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
@@ -796,10 +778,10 @@
         <v>17.15</v>
       </c>
       <c r="U4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="V4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
@@ -819,28 +801,28 @@
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>14460</v>
+        <v>170</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I5" s="3">
-        <v>104.99</v>
+        <v>14.9</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
       </c>
       <c r="K5" s="3">
-        <v>23.91</v>
+        <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -849,22 +831,22 @@
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <v>97.83</v>
+        <v>14.9</v>
       </c>
       <c r="S5" s="3">
         <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>97.83</v>
+        <v>14.9</v>
       </c>
       <c r="U5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="V5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -881,57 +863,57 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>14460</v>
+        <v>170</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I6" s="3">
-        <v>104.99</v>
+        <v>14.9</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
       </c>
       <c r="K6" s="3">
-        <v>23.91</v>
+        <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="3">
-        <v>23.48</v>
+        <v>14.9</v>
       </c>
       <c r="S6" s="3">
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>23.48</v>
+        <v>14.9</v>
       </c>
       <c r="U6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="V6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>23</v>
@@ -943,28 +925,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3">
-        <v>104.99</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
       </c>
       <c r="K7" s="3">
-        <v>23.91</v>
+        <v>16.63</v>
       </c>
       <c r="N7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -973,19 +955,19 @@
         <v>0</v>
       </c>
       <c r="R7" s="3">
-        <v>7.16</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="S7" s="3">
         <v>0</v>
       </c>
       <c r="T7" s="3">
-        <v>7.16</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="U7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
@@ -993,7 +975,7 @@
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>23</v>
@@ -1005,28 +987,28 @@
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3">
-        <v>104.99</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>23.91</v>
+        <v>16.63</v>
       </c>
       <c r="N8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1035,19 +1017,19 @@
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>0.43</v>
+        <v>16.63</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>0.43</v>
+        <v>16.63</v>
       </c>
       <c r="U8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
@@ -1055,7 +1037,7 @@
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>23</v>
@@ -1067,28 +1049,28 @@
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3">
-        <v>104.99</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>23.91</v>
+        <v>16.63</v>
       </c>
       <c r="N9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -1097,331 +1079,21 @@
         <v>1</v>
       </c>
       <c r="R9" s="3">
-        <v>104.99</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="S9" s="3">
-        <v>23.91</v>
+        <v>16.63</v>
       </c>
       <c r="T9" s="3">
-        <v>128.9</v>
+        <v>85.92</v>
       </c>
       <c r="U9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="W9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10" s="1">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>170</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>42</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="U10" t="s">
-        <v>33</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="W10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11" s="1">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>170</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>1</v>
-      </c>
-      <c r="R11" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="S11" s="3">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="U11" t="s">
-        <v>33</v>
-      </c>
-      <c r="V11" t="s">
-        <v>30</v>
-      </c>
-      <c r="W11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="A12" s="1">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="3">
-        <v>-33.06</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>-7.93</v>
-      </c>
-      <c r="N12" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <v>-33.06</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3">
-        <v>-33.06</v>
-      </c>
-      <c r="U12" t="s">
-        <v>34</v>
-      </c>
-      <c r="V12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
-      <c r="A13" s="1">
-        <v>4</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="3">
-        <v>-33.06</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
-        <v>-7.93</v>
-      </c>
-      <c r="N13" t="s">
-        <v>39</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3">
-        <v>-7.93</v>
-      </c>
-      <c r="S13" s="3">
-        <v>0</v>
-      </c>
-      <c r="T13" s="3">
-        <v>-7.93</v>
-      </c>
-      <c r="U13" t="s">
-        <v>34</v>
-      </c>
-      <c r="V13" t="s">
-        <v>29</v>
-      </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
-      <c r="A14" s="1">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-33.06</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-7.93</v>
-      </c>
-      <c r="N14" t="s">
-        <v>37</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>1</v>
-      </c>
-      <c r="R14" s="3">
-        <v>-33.06</v>
-      </c>
-      <c r="S14" s="3">
-        <v>-7.93</v>
-      </c>
-      <c r="T14" s="3">
-        <v>-40.99</v>
-      </c>
-      <c r="U14" t="s">
-        <v>34</v>
-      </c>
-      <c r="V14" t="s">
-        <v>29</v>
-      </c>
-      <c r="W14" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1432,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -1442,13 +1114,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1456,32 +1128,21 @@
         <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>20254</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="36">
   <si>
     <t>ARTID</t>
   </si>
@@ -86,51 +86,33 @@
     <t>OTHEREXPEND</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>03/10/2025</t>
-  </si>
-  <si>
-    <t>15/09/2025</t>
-  </si>
-  <si>
-    <t>12/11/2025</t>
-  </si>
-  <si>
-    <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
-  </si>
-  <si>
-    <t>801466788</t>
-  </si>
-  <si>
-    <t>12Μ0ΤΔΑ 10768</t>
-  </si>
-  <si>
-    <t>ΑΛΠ 61010</t>
-  </si>
-  <si>
-    <t>11Μ0ΤΔΑ 9480</t>
-  </si>
-  <si>
-    <t>64-98-99-0087</t>
-  </si>
-  <si>
-    <t>63-98-08-0000</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>ΑΦΟΙ ΛΑΓΟΥ ΧΡΩΜΑΤΑ ΙΚΕ</t>
+  </si>
+  <si>
+    <t>TΔA 60984</t>
+  </si>
+  <si>
+    <t>20-02-00-0024</t>
+  </si>
+  <si>
+    <t>54-02-02-2024</t>
+  </si>
+  <si>
+    <t>20-02-00-0006</t>
+  </si>
+  <si>
+    <t>54-02-02-2006</t>
   </si>
   <si>
     <t>50-00-00-0000</t>
   </si>
   <si>
-    <t>64-12-00-0000</t>
-  </si>
-  <si>
-    <t>20-02-00-0024</t>
-  </si>
-  <si>
-    <t>54-02-02-2024</t>
-  </si>
-  <si>
     <t>Α/Α</t>
   </si>
   <si>
@@ -140,13 +122,7 @@
     <t>ΕΠΩΝΥΜΙΑ</t>
   </si>
   <si>
-    <t>000000000</t>
-  </si>
-  <si>
-    <t>094439854</t>
-  </si>
-  <si>
-    <t>ΠΡΟΜΗΘΕΥΤΕΣ ΔΑΠΑΝΩΝ</t>
+    <t>800916954</t>
   </si>
 </sst>
 </file>
@@ -511,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -615,29 +591,29 @@
         <v>0</v>
       </c>
       <c r="E2" s="1">
-        <v>20254</v>
+        <v>14460</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3">
+        <v>104.99</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="3">
-        <v>13.83</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3">
-        <v>3.32</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
       <c r="O2" s="1">
         <v>0</v>
       </c>
@@ -645,19 +621,19 @@
         <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>13.83</v>
+        <v>97.83</v>
       </c>
       <c r="S2" s="3">
         <v>0</v>
       </c>
       <c r="T2" s="3">
-        <v>13.83</v>
+        <v>97.83</v>
       </c>
       <c r="U2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="W2" s="1">
         <v>0</v>
@@ -677,28 +653,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>20254</v>
+        <v>14460</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3">
-        <v>13.83</v>
+        <v>104.99</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
       </c>
       <c r="K3" s="3">
-        <v>3.32</v>
+        <v>23.91</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -707,19 +683,19 @@
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <v>3.32</v>
+        <v>23.48</v>
       </c>
       <c r="S3" s="3">
         <v>0</v>
       </c>
       <c r="T3" s="3">
-        <v>3.32</v>
+        <v>23.48</v>
       </c>
       <c r="U3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -739,49 +715,49 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>20254</v>
+        <v>14460</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3">
+        <v>104.99</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="N4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="3">
-        <v>13.83</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3">
-        <v>3.32</v>
-      </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
       <c r="O4" s="1">
         <v>0</v>
       </c>
       <c r="Q4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="3">
-        <v>13.83</v>
+        <v>7.16</v>
       </c>
       <c r="S4" s="3">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>17.15</v>
+        <v>7.16</v>
       </c>
       <c r="U4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
@@ -789,7 +765,7 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
@@ -801,29 +777,29 @@
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="3">
+        <v>104.99</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="N5" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="3">
-        <v>14.9</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>35</v>
-      </c>
       <c r="O5" s="1">
         <v>0</v>
       </c>
@@ -831,27 +807,27 @@
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <v>14.9</v>
+        <v>0.43</v>
       </c>
       <c r="S5" s="3">
         <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>14.9</v>
+        <v>0.43</v>
       </c>
       <c r="U5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="V5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="W5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -863,28 +839,28 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I6" s="3">
-        <v>14.9</v>
+        <v>104.99</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -893,207 +869,21 @@
         <v>1</v>
       </c>
       <c r="R6" s="3">
-        <v>14.9</v>
+        <v>104.99</v>
       </c>
       <c r="S6" s="3">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="T6" s="3">
-        <v>14.9</v>
+        <v>128.9</v>
       </c>
       <c r="U6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="V6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="W6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>20254</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="N7" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="S7" s="3">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="U7" t="s">
-        <v>31</v>
-      </c>
-      <c r="V7" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8" s="1">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>20254</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="N8" t="s">
-        <v>37</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="U8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V8" t="s">
-        <v>27</v>
-      </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>20254</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="N9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="S9" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="T9" s="3">
-        <v>85.92</v>
-      </c>
-      <c r="U9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V9" t="s">
-        <v>27</v>
-      </c>
-      <c r="W9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1104,7 +894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -1114,35 +904,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>20254</v>
-      </c>
-      <c r="B3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t>ARTID</t>
   </si>
@@ -89,28 +89,49 @@
     <t>15</t>
   </si>
   <si>
+    <t>12/11/2025</t>
+  </si>
+  <si>
     <t>11/11/2025</t>
   </si>
   <si>
+    <t>10/10/2025</t>
+  </si>
+  <si>
+    <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
+  </si>
+  <si>
     <t>ΑΦΟΙ ΛΑΓΟΥ ΧΡΩΜΑΤΑ ΙΚΕ</t>
   </si>
   <si>
+    <t>ΤΕΡΖΟΠΟΥΛΟΣ ΚΩΝΣΤ (115333562)</t>
+  </si>
+  <si>
+    <t>11Μ0ΤΔΑ 9480</t>
+  </si>
+  <si>
     <t>TΔA 60984</t>
   </si>
   <si>
+    <t>ΑΛΠ 36671</t>
+  </si>
+  <si>
     <t>20-02-00-0024</t>
   </si>
   <si>
     <t>54-02-02-2024</t>
   </si>
   <si>
+    <t>50-00-00-0000</t>
+  </si>
+  <si>
     <t>20-02-00-0006</t>
   </si>
   <si>
     <t>54-02-02-2006</t>
   </si>
   <si>
-    <t>50-00-00-0000</t>
+    <t>64-12-00-0000</t>
   </si>
   <si>
     <t>Α/Α</t>
@@ -122,7 +143,16 @@
     <t>ΕΠΩΝΥΜΙΑ</t>
   </si>
   <si>
+    <t>000000000</t>
+  </si>
+  <si>
     <t>800916954</t>
+  </si>
+  <si>
+    <t>094439854</t>
+  </si>
+  <si>
+    <t>ΠΡΟΜΗΘΕΥΤΕΣ ΔΑΠΑΝΩΝ</t>
   </si>
 </sst>
 </file>
@@ -487,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -591,49 +621,49 @@
         <v>0</v>
       </c>
       <c r="E2" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3">
-        <v>104.99</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
       </c>
       <c r="K2" s="3">
-        <v>23.91</v>
+        <v>16.63</v>
       </c>
       <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="U2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" t="s">
         <v>27</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3">
-        <v>97.83</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3">
-        <v>97.83</v>
-      </c>
-      <c r="U2" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" t="s">
-        <v>25</v>
       </c>
       <c r="W2" s="1">
         <v>0</v>
@@ -653,28 +683,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I3" s="3">
-        <v>104.99</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
       </c>
       <c r="K3" s="3">
-        <v>23.91</v>
+        <v>16.63</v>
       </c>
       <c r="N3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -683,19 +713,19 @@
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <v>23.48</v>
+        <v>16.63</v>
       </c>
       <c r="S3" s="3">
         <v>0</v>
       </c>
       <c r="T3" s="3">
-        <v>23.48</v>
+        <v>16.63</v>
       </c>
       <c r="U3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="V3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -715,49 +745,49 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>14460</v>
+        <v>20254</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I4" s="3">
-        <v>104.99</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
       </c>
       <c r="K4" s="3">
-        <v>23.91</v>
+        <v>16.63</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
       </c>
       <c r="Q4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="3">
-        <v>7.16</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="S4" s="3">
-        <v>0</v>
+        <v>16.63</v>
       </c>
       <c r="T4" s="3">
-        <v>7.16</v>
+        <v>85.92</v>
       </c>
       <c r="U4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="V4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
@@ -765,7 +795,7 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
@@ -780,13 +810,13 @@
         <v>14460</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3">
         <v>104.99</v>
@@ -798,7 +828,7 @@
         <v>23.91</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -807,19 +837,19 @@
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <v>0.43</v>
+        <v>97.83</v>
       </c>
       <c r="S5" s="3">
         <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>0.43</v>
+        <v>97.83</v>
       </c>
       <c r="U5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="V5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
@@ -827,7 +857,7 @@
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -842,13 +872,13 @@
         <v>14460</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3">
         <v>104.99</v>
@@ -860,31 +890,341 @@
         <v>23.91</v>
       </c>
       <c r="N6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <v>23.48</v>
+      </c>
+      <c r="S6" s="3">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
+        <v>23.48</v>
+      </c>
+      <c r="U6" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3">
+      <c r="V6" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>14460</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3">
         <v>104.99</v>
       </c>
-      <c r="S6" s="3">
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
         <v>23.91</v>
       </c>
-      <c r="T6" s="3">
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>7.16</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3">
+        <v>7.16</v>
+      </c>
+      <c r="U7" t="s">
+        <v>31</v>
+      </c>
+      <c r="V7" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>14460</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3">
+        <v>104.99</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="N8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="U8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V8" t="s">
+        <v>28</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>14460</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3">
+        <v>104.99</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="N9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3">
+        <v>104.99</v>
+      </c>
+      <c r="S9" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="T9" s="3">
         <v>128.9</v>
       </c>
-      <c r="U6" t="s">
+      <c r="U9" t="s">
+        <v>31</v>
+      </c>
+      <c r="V9" t="s">
+        <v>28</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>170</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="V6" t="s">
-        <v>25</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>8</v>
+      </c>
+      <c r="U10" t="s">
+        <v>32</v>
+      </c>
+      <c r="V10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>170</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3">
+        <v>8</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3">
+        <v>8</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
+        <v>8</v>
+      </c>
+      <c r="U11" t="s">
+        <v>32</v>
+      </c>
+      <c r="V11" t="s">
+        <v>29</v>
+      </c>
+      <c r="W11" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -894,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -904,24 +1244,46 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
+        <v>170</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
         <v>14460</v>
       </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>20254</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="43">
   <si>
     <t>ARTID</t>
   </si>
@@ -95,16 +95,13 @@
     <t>11/11/2025</t>
   </si>
   <si>
-    <t>10/10/2025</t>
-  </si>
-  <si>
     <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
   </si>
   <si>
     <t>ΑΦΟΙ ΛΑΓΟΥ ΧΡΩΜΑΤΑ ΙΚΕ</t>
   </si>
   <si>
-    <t>ΤΕΡΖΟΠΟΥΛΟΣ ΚΩΝΣΤ (115333562)</t>
+    <t>K. &amp; E. ΠΑΥΛΑΤΟΥ O.Ε.</t>
   </si>
   <si>
     <t>11Μ0ΤΔΑ 9480</t>
@@ -113,7 +110,7 @@
     <t>TΔA 60984</t>
   </si>
   <si>
-    <t>ΑΛΠ 36671</t>
+    <t>ΤΙΠΕ 13241</t>
   </si>
   <si>
     <t>20-02-00-0024</t>
@@ -131,9 +128,6 @@
     <t>54-02-02-2006</t>
   </si>
   <si>
-    <t>64-12-00-0000</t>
-  </si>
-  <si>
     <t>Α/Α</t>
   </si>
   <si>
@@ -143,16 +137,13 @@
     <t>ΕΠΩΝΥΜΙΑ</t>
   </si>
   <si>
-    <t>000000000</t>
+    <t>997751666</t>
   </si>
   <si>
     <t>800916954</t>
   </si>
   <si>
     <t>094439854</t>
-  </si>
-  <si>
-    <t>ΠΡΟΜΗΘΕΥΤΕΣ ΔΑΠΑΝΩΝ</t>
   </si>
 </sst>
 </file>
@@ -517,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -627,10 +618,10 @@
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" s="3">
         <v>69.29000000000001</v>
@@ -642,7 +633,7 @@
         <v>16.63</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -660,10 +651,10 @@
         <v>69.29000000000001</v>
       </c>
       <c r="U2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W2" s="1">
         <v>0</v>
@@ -689,10 +680,10 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3">
         <v>69.29000000000001</v>
@@ -704,7 +695,7 @@
         <v>16.63</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -722,10 +713,10 @@
         <v>16.63</v>
       </c>
       <c r="U3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -751,10 +742,10 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3">
         <v>69.29000000000001</v>
@@ -766,7 +757,7 @@
         <v>16.63</v>
       </c>
       <c r="N4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
@@ -784,10 +775,10 @@
         <v>85.92</v>
       </c>
       <c r="U4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
@@ -813,10 +804,10 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" s="3">
         <v>104.99</v>
@@ -828,7 +819,7 @@
         <v>23.91</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -846,10 +837,10 @@
         <v>97.83</v>
       </c>
       <c r="U5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
@@ -875,10 +866,10 @@
         <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" s="3">
         <v>104.99</v>
@@ -890,7 +881,7 @@
         <v>23.91</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -908,10 +899,10 @@
         <v>23.48</v>
       </c>
       <c r="U6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
@@ -937,10 +928,10 @@
         <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3">
         <v>104.99</v>
@@ -952,7 +943,7 @@
         <v>23.91</v>
       </c>
       <c r="N7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -970,10 +961,10 @@
         <v>7.16</v>
       </c>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
@@ -999,10 +990,10 @@
         <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3">
         <v>104.99</v>
@@ -1014,7 +1005,7 @@
         <v>23.91</v>
       </c>
       <c r="N8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1032,10 +1023,10 @@
         <v>0.43</v>
       </c>
       <c r="U8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
@@ -1061,10 +1052,10 @@
         <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="3">
         <v>104.99</v>
@@ -1076,7 +1067,7 @@
         <v>23.91</v>
       </c>
       <c r="N9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -1094,10 +1085,10 @@
         <v>128.9</v>
       </c>
       <c r="U9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
@@ -1117,29 +1108,29 @@
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>170</v>
+        <v>9135</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3">
+        <v>240.32</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>57.68</v>
+      </c>
+      <c r="N10" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="3">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>38</v>
-      </c>
       <c r="O10" s="1">
         <v>0</v>
       </c>
@@ -1147,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>8</v>
+        <v>240.32</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
       <c r="T10" s="3">
-        <v>8</v>
+        <v>240.32</v>
       </c>
       <c r="U10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -1179,52 +1170,114 @@
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>170</v>
+        <v>9135</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3">
-        <v>8</v>
+        <v>240.32</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>57.68</v>
       </c>
       <c r="N11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
       </c>
       <c r="Q11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="3">
-        <v>8</v>
+        <v>57.68</v>
       </c>
       <c r="S11" s="3">
         <v>0</v>
       </c>
       <c r="T11" s="3">
-        <v>8</v>
+        <v>57.68</v>
       </c>
       <c r="U11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W11" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="1">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>9135</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3">
+        <v>240.32</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>57.68</v>
+      </c>
+      <c r="N12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1</v>
+      </c>
+      <c r="R12" s="3">
+        <v>240.32</v>
+      </c>
+      <c r="S12" s="3">
+        <v>57.68</v>
+      </c>
+      <c r="T12" s="3">
+        <v>298</v>
+      </c>
+      <c r="U12" t="s">
+        <v>31</v>
+      </c>
+      <c r="V12" t="s">
+        <v>28</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1244,24 +1297,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>170</v>
+        <v>9135</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1269,10 +1322,10 @@
         <v>14460</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1280,10 +1333,10 @@
         <v>20254</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>ARTID</t>
   </si>
@@ -86,31 +86,16 @@
     <t>OTHEREXPEND</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>12/11/2025</t>
-  </si>
-  <si>
-    <t>11/11/2025</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>24/11/2025</t>
   </si>
   <si>
     <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
   </si>
   <si>
-    <t>ΑΦΟΙ ΛΑΓΟΥ ΧΡΩΜΑΤΑ ΙΚΕ</t>
-  </si>
-  <si>
-    <t>K. &amp; E. ΠΑΥΛΑΤΟΥ O.Ε.</t>
-  </si>
-  <si>
-    <t>11Μ0ΤΔΑ 9480</t>
-  </si>
-  <si>
-    <t>TΔA 60984</t>
-  </si>
-  <si>
-    <t>ΤΙΠΕ 13241</t>
+    <t>11Μ0ΤΔΑ 9953</t>
   </si>
   <si>
     <t>20-02-00-0024</t>
@@ -122,12 +107,6 @@
     <t>50-00-00-0000</t>
   </si>
   <si>
-    <t>20-02-00-0006</t>
-  </si>
-  <si>
-    <t>54-02-02-2006</t>
-  </si>
-  <si>
     <t>Α/Α</t>
   </si>
   <si>
@@ -135,12 +114,6 @@
   </si>
   <si>
     <t>ΕΠΩΝΥΜΙΑ</t>
-  </si>
-  <si>
-    <t>997751666</t>
-  </si>
-  <si>
-    <t>800916954</t>
   </si>
   <si>
     <t>094439854</t>
@@ -508,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -606,10 +579,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="1">
         <v>20254</v>
@@ -618,43 +588,40 @@
         <v>24</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
       <c r="I2" s="3">
-        <v>69.29000000000001</v>
+        <v>45.68</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
       </c>
       <c r="K2" s="3">
-        <v>16.63</v>
+        <v>10.96</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>69.29000000000001</v>
+        <v>45.68</v>
       </c>
       <c r="S2" s="3">
         <v>0</v>
       </c>
       <c r="T2" s="3">
-        <v>69.29000000000001</v>
+        <v>45.68</v>
       </c>
       <c r="U2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="1">
         <v>0</v>
@@ -668,10 +635,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
         <v>20254</v>
@@ -680,22 +644,22 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
       <c r="I3" s="3">
-        <v>69.29000000000001</v>
+        <v>45.68</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
       </c>
       <c r="K3" s="3">
-        <v>16.63</v>
+        <v>10.96</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -704,19 +668,19 @@
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <v>16.63</v>
+        <v>10.96</v>
       </c>
       <c r="S3" s="3">
         <v>0</v>
       </c>
       <c r="T3" s="3">
-        <v>16.63</v>
+        <v>10.96</v>
       </c>
       <c r="U3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -730,10 +694,7 @@
         <v>23</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
         <v>20254</v>
@@ -742,541 +703,42 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" s="3">
+        <v>45.68</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>10.96</v>
+      </c>
+      <c r="N4" t="s">
         <v>29</v>
-      </c>
-      <c r="I4" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="1">
-        <v>0</v>
       </c>
       <c r="Q4" s="1">
         <v>1</v>
       </c>
       <c r="R4" s="3">
-        <v>69.29000000000001</v>
+        <v>56.64</v>
       </c>
       <c r="S4" s="3">
-        <v>16.63</v>
+        <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>85.92</v>
+        <v>56.64</v>
       </c>
       <c r="U4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3">
-        <v>97.83</v>
-      </c>
-      <c r="S5" s="3">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3">
-        <v>97.83</v>
-      </c>
-      <c r="U5" t="s">
-        <v>30</v>
-      </c>
-      <c r="V5" t="s">
-        <v>27</v>
-      </c>
-      <c r="W5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <v>23.48</v>
-      </c>
-      <c r="S6" s="3">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
-        <v>23.48</v>
-      </c>
-      <c r="U6" t="s">
-        <v>30</v>
-      </c>
-      <c r="V6" t="s">
-        <v>27</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <v>7.16</v>
-      </c>
-      <c r="S7" s="3">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3">
-        <v>7.16</v>
-      </c>
-      <c r="U7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V7" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0.43</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0.43</v>
-      </c>
-      <c r="U8" t="s">
-        <v>30</v>
-      </c>
-      <c r="V8" t="s">
-        <v>27</v>
-      </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="S9" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="T9" s="3">
-        <v>128.9</v>
-      </c>
-      <c r="U9" t="s">
-        <v>30</v>
-      </c>
-      <c r="V9" t="s">
-        <v>27</v>
-      </c>
-      <c r="W9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10" s="1">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>9135</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3">
-        <v>240.32</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>57.68</v>
-      </c>
-      <c r="N10" t="s">
-        <v>32</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3">
-        <v>240.32</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <v>240.32</v>
-      </c>
-      <c r="U10" t="s">
-        <v>31</v>
-      </c>
-      <c r="V10" t="s">
-        <v>28</v>
-      </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11" s="1">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>9135</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3">
-        <v>240.32</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>57.68</v>
-      </c>
-      <c r="N11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
-        <v>57.68</v>
-      </c>
-      <c r="S11" s="3">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>57.68</v>
-      </c>
-      <c r="U11" t="s">
-        <v>31</v>
-      </c>
-      <c r="V11" t="s">
-        <v>28</v>
-      </c>
-      <c r="W11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="A12" s="1">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>9135</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3">
-        <v>240.32</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>57.68</v>
-      </c>
-      <c r="N12" t="s">
-        <v>34</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>1</v>
-      </c>
-      <c r="R12" s="3">
-        <v>240.32</v>
-      </c>
-      <c r="S12" s="3">
-        <v>57.68</v>
-      </c>
-      <c r="T12" s="3">
-        <v>298</v>
-      </c>
-      <c r="U12" t="s">
-        <v>31</v>
-      </c>
-      <c r="V12" t="s">
-        <v>28</v>
-      </c>
-      <c r="W12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1287,7 +749,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -1297,46 +759,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>9135</v>
+        <v>20254</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>14460</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>20254</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
     <t>ARTID</t>
   </si>
@@ -86,18 +86,30 @@
     <t>OTHEREXPEND</t>
   </si>
   <si>
-    <t>1</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>24/11/2025</t>
   </si>
   <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
     <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
   </si>
   <si>
+    <t>ROX COFFEE COMPANY ΕΤΕΡΟΡΡΥΘΜΗ ΕΤΑΙΡΕΙΑ (801466788)</t>
+  </si>
+  <si>
     <t>11Μ0ΤΔΑ 9953</t>
   </si>
   <si>
+    <t>ΑΛΠ 61010</t>
+  </si>
+  <si>
     <t>20-02-00-0024</t>
   </si>
   <si>
@@ -107,6 +119,9 @@
     <t>50-00-00-0000</t>
   </si>
   <si>
+    <t>64-12-00-0000</t>
+  </si>
+  <si>
     <t>Α/Α</t>
   </si>
   <si>
@@ -116,7 +131,13 @@
     <t>ΕΠΩΝΥΜΙΑ</t>
   </si>
   <si>
+    <t>000000000</t>
+  </si>
+  <si>
     <t>094439854</t>
+  </si>
+  <si>
+    <t>ΠΡΟΜΗΘΕΥΤΕΣ ΔΑΠΑΝΩΝ</t>
   </si>
 </sst>
 </file>
@@ -481,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -585,13 +606,13 @@
         <v>20254</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I2" s="3">
         <v>45.68</v>
@@ -603,7 +624,7 @@
         <v>10.96</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
@@ -618,10 +639,10 @@
         <v>45.68</v>
       </c>
       <c r="U2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W2" s="1">
         <v>0</v>
@@ -641,13 +662,13 @@
         <v>20254</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3">
         <v>45.68</v>
@@ -659,7 +680,7 @@
         <v>10.96</v>
       </c>
       <c r="N3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -677,10 +698,10 @@
         <v>10.96</v>
       </c>
       <c r="U3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -700,13 +721,13 @@
         <v>20254</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3">
         <v>45.68</v>
@@ -718,7 +739,7 @@
         <v>10.96</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q4" s="1">
         <v>1</v>
@@ -733,13 +754,125 @@
         <v>56.64</v>
       </c>
       <c r="U4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>170</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="V4" t="s">
-        <v>25</v>
-      </c>
-      <c r="W4" s="1">
-        <v>0</v>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="S5" s="3">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="U5" t="s">
+        <v>30</v>
+      </c>
+      <c r="V5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>170</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="S6" s="3">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="U6" t="s">
+        <v>30</v>
+      </c>
+      <c r="V6" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -759,24 +892,35 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
+        <v>170</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
         <v>20254</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -602,6 +602,9 @@
       <c r="C2" s="1">
         <v>2</v>
       </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
       <c r="E2" s="1">
         <v>20254</v>
       </c>
@@ -658,6 +661,9 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
       <c r="E3" s="1">
         <v>20254</v>
       </c>
@@ -717,6 +723,9 @@
       <c r="C4" s="1">
         <v>2</v>
       </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
       <c r="E4" s="1">
         <v>20254</v>
       </c>
@@ -773,6 +782,9 @@
       <c r="C5" s="1">
         <v>2</v>
       </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
       <c r="E5" s="1">
         <v>170</v>
       </c>
@@ -828,6 +840,9 @@
       </c>
       <c r="C6" s="1">
         <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>170</v>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="42">
   <si>
     <t>ARTID</t>
   </si>
@@ -89,69 +89,24 @@
     <t>1</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>15</t>
   </si>
   <si>
     <t>01/12/2025</t>
   </si>
   <si>
-    <t>30/10/2025</t>
-  </si>
-  <si>
-    <t>10/10/2025</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>10/11/2025</t>
-  </si>
-  <si>
-    <t>12/11/2025</t>
-  </si>
-  <si>
     <t>11/11/2025</t>
   </si>
   <si>
     <t>GALAXY HELLAS ΕΜΠΟΡΙΚΗ – ΕΙΣΑΓΩΓΙΚΗ Ε.Ε.</t>
   </si>
   <si>
-    <t>KOUTSI KATSIKA STREETFOOD ΓΛΥΦΑΔΑ Ε Ε (802673972)</t>
-  </si>
-  <si>
-    <t>ΤΕΡΖΟΠΟΥΛΟΣ ΚΩΝΣΤ (115333562)</t>
-  </si>
-  <si>
-    <t>PREMIER CAPITAL ΕΛΛΑΣ-Διαχείριση και Λειτουργία Εστιατορίων ΜΟΝΟΠΡΟΣΩΠΗ ΑΝΩΝΥΜΗ ΕΤΑΙΡΕΙΑ (094386010)</t>
-  </si>
-  <si>
     <t>ΑΦΟΙ ΛΑΓΟΥ ΧΡΩΜΑΤΑ ΙΚΕ</t>
   </si>
   <si>
-    <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
-  </si>
-  <si>
     <t>ΤΔΑ 4653</t>
   </si>
   <si>
-    <t>ΑΛΠ 83115</t>
-  </si>
-  <si>
-    <t>ΑΛΠ 36671</t>
-  </si>
-  <si>
-    <t>ΑΛΠ 165</t>
-  </si>
-  <si>
-    <t>TΔA 60939</t>
-  </si>
-  <si>
-    <t>11Μ0ΤΔΑ 9480</t>
-  </si>
-  <si>
     <t>TΔA 60984</t>
   </si>
   <si>
@@ -164,13 +119,13 @@
     <t>50-00-00-0000</t>
   </si>
   <si>
-    <t>64-12-00-0000</t>
-  </si>
-  <si>
-    <t>64-12-00-0006</t>
-  </si>
-  <si>
-    <t>54-02-02-6006</t>
+    <t>24-02-00-0024</t>
+  </si>
+  <si>
+    <t>64-98-99-0025</t>
+  </si>
+  <si>
+    <t>63-98-08-0000</t>
   </si>
   <si>
     <t>Α/Α</t>
@@ -182,19 +137,10 @@
     <t>ΕΠΩΝΥΜΙΑ</t>
   </si>
   <si>
-    <t>000000000</t>
-  </si>
-  <si>
     <t>800916954</t>
   </si>
   <si>
-    <t>094439854</t>
-  </si>
-  <si>
     <t>800470153</t>
-  </si>
-  <si>
-    <t>ΠΡΟΜΗΘΕΥΤΕΣ ΔΑΠΑΝΩΝ</t>
   </si>
 </sst>
 </file>
@@ -559,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -666,13 +612,13 @@
         <v>142076</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I2" s="3">
         <v>24.06</v>
@@ -684,7 +630,7 @@
         <v>5.77</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
@@ -699,10 +645,10 @@
         <v>24.06</v>
       </c>
       <c r="U2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="V2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="W2" s="1">
         <v>0</v>
@@ -725,13 +671,13 @@
         <v>142076</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3">
         <v>24.06</v>
@@ -743,7 +689,7 @@
         <v>5.77</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -761,10 +707,10 @@
         <v>5.77</v>
       </c>
       <c r="U3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -787,13 +733,13 @@
         <v>142076</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3">
         <v>24.06</v>
@@ -805,7 +751,7 @@
         <v>5.77</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="Q4" s="1">
         <v>1</v>
@@ -820,10 +766,10 @@
         <v>29.83</v>
       </c>
       <c r="U4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="V4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
@@ -843,49 +789,49 @@
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <v>104.99</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="N5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="3">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>49</v>
-      </c>
       <c r="Q5" s="1">
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <v>9.300000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="S5" s="3">
         <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>9.300000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="U5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="V5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -902,54 +848,57 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I6" s="3">
-        <v>9.300000000000001</v>
+        <v>104.99</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>32</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3">
-        <v>9.300000000000001</v>
+        <v>23.48</v>
       </c>
       <c r="S6" s="3">
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>9.300000000000001</v>
+        <v>23.48</v>
       </c>
       <c r="U6" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="V6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>24</v>
@@ -961,54 +910,54 @@
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
         <v>28</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3">
+        <v>104.99</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="N7" t="s">
         <v>35</v>
       </c>
-      <c r="H7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="3">
-        <v>8</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>49</v>
-      </c>
       <c r="Q7" s="1">
         <v>0</v>
       </c>
       <c r="R7" s="3">
-        <v>8</v>
+        <v>7.16</v>
       </c>
       <c r="S7" s="3">
         <v>0</v>
       </c>
       <c r="T7" s="3">
-        <v>8</v>
+        <v>7.16</v>
       </c>
       <c r="U7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="V7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>24</v>
@@ -1020,54 +969,57 @@
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3">
-        <v>8</v>
+        <v>104.99</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="N8" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
       </c>
       <c r="Q8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>8</v>
+        <v>0.43</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>8</v>
+        <v>0.43</v>
       </c>
       <c r="U8" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="V8" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>24</v>
@@ -1079,768 +1031,48 @@
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="I9" s="3">
-        <v>9.4</v>
+        <v>104.99</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="N9" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="Q9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="3">
-        <v>9.4</v>
+        <v>128.9</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>9.4</v>
+        <v>128.9</v>
       </c>
       <c r="U9" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="V9" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="W9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10" s="1">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>170</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="U10" t="s">
-        <v>42</v>
-      </c>
-      <c r="V10" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="3">
-        <v>33.06</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>7.93</v>
-      </c>
-      <c r="N11" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
-        <v>33.06</v>
-      </c>
-      <c r="S11" s="3">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>33.06</v>
-      </c>
-      <c r="U11" t="s">
-        <v>43</v>
-      </c>
-      <c r="V11" t="s">
-        <v>37</v>
-      </c>
-      <c r="W11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="A12" s="1">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="3">
-        <v>33.06</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>7.93</v>
-      </c>
-      <c r="N12" t="s">
-        <v>47</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <v>7.93</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3">
-        <v>7.93</v>
-      </c>
-      <c r="U12" t="s">
-        <v>43</v>
-      </c>
-      <c r="V12" t="s">
-        <v>37</v>
-      </c>
-      <c r="W12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
-      <c r="A13" s="1">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="3">
-        <v>33.06</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
-        <v>7.93</v>
-      </c>
-      <c r="N13" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>1</v>
-      </c>
-      <c r="R13" s="3">
-        <v>40.99</v>
-      </c>
-      <c r="S13" s="3">
-        <v>0</v>
-      </c>
-      <c r="T13" s="3">
-        <v>40.99</v>
-      </c>
-      <c r="U13" t="s">
-        <v>43</v>
-      </c>
-      <c r="V13" t="s">
-        <v>37</v>
-      </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
-      <c r="A14" s="1">
-        <v>6</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>20254</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="N14" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="U14" t="s">
-        <v>44</v>
-      </c>
-      <c r="V14" t="s">
-        <v>38</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23">
-      <c r="A15" s="1">
-        <v>6</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>20254</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="N15" t="s">
-        <v>47</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="U15" t="s">
-        <v>44</v>
-      </c>
-      <c r="V15" t="s">
-        <v>38</v>
-      </c>
-      <c r="W15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23">
-      <c r="A16" s="1">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
-        <v>20254</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="3">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="J16" s="3">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3">
-        <v>16.63</v>
-      </c>
-      <c r="N16" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3">
-        <v>85.92</v>
-      </c>
-      <c r="S16" s="3">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3">
-        <v>85.92</v>
-      </c>
-      <c r="U16" t="s">
-        <v>44</v>
-      </c>
-      <c r="V16" t="s">
-        <v>38</v>
-      </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
-      <c r="A17" s="1">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="1">
-        <v>2</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="3">
-        <v>209.98</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>47.82</v>
-      </c>
-      <c r="N17" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3">
-        <v>195.66</v>
-      </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3">
-        <v>195.66</v>
-      </c>
-      <c r="U17" t="s">
-        <v>45</v>
-      </c>
-      <c r="V17" t="s">
-        <v>37</v>
-      </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
-      <c r="A18" s="1">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="1">
-        <v>2</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="3">
-        <v>209.98</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>47.82</v>
-      </c>
-      <c r="N18" t="s">
-        <v>47</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
-        <v>46.96</v>
-      </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
-        <v>46.96</v>
-      </c>
-      <c r="U18" t="s">
-        <v>45</v>
-      </c>
-      <c r="V18" t="s">
-        <v>37</v>
-      </c>
-      <c r="W18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="1">
-        <v>7</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="3">
-        <v>209.98</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3">
-        <v>47.82</v>
-      </c>
-      <c r="N19" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="3">
-        <v>14.32</v>
-      </c>
-      <c r="S19" s="3">
-        <v>0</v>
-      </c>
-      <c r="T19" s="3">
-        <v>14.32</v>
-      </c>
-      <c r="U19" t="s">
-        <v>45</v>
-      </c>
-      <c r="V19" t="s">
-        <v>37</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="1">
-        <v>7</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="1">
-        <v>2</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="3">
-        <v>209.98</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>47.82</v>
-      </c>
-      <c r="N20" t="s">
-        <v>51</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0.86</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0.86</v>
-      </c>
-      <c r="U20" t="s">
-        <v>45</v>
-      </c>
-      <c r="V20" t="s">
-        <v>37</v>
-      </c>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="1">
-        <v>7</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="1">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="3">
-        <v>209.98</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>47.82</v>
-      </c>
-      <c r="N21" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>1</v>
-      </c>
-      <c r="R21" s="3">
-        <v>257.8</v>
-      </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3">
-        <v>257.8</v>
-      </c>
-      <c r="U21" t="s">
-        <v>45</v>
-      </c>
-      <c r="V21" t="s">
-        <v>37</v>
-      </c>
-      <c r="W21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1851,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -1861,57 +1093,35 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>170</v>
+        <v>14460</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>14460</v>
+        <v>142076</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>20254</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
-        <v>142076</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
+++ b/data/tony/exports/802576637_G_CATEGORY_EPSILON_BRIDGE_KINHSEIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>ARTID</t>
   </si>
@@ -86,48 +86,24 @@
     <t>OTHEREXPEND</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>3</t>
   </si>
   <si>
     <t>01/12/2025</t>
   </si>
   <si>
-    <t>11/11/2025</t>
-  </si>
-  <si>
     <t>GALAXY HELLAS ΕΜΠΟΡΙΚΗ – ΕΙΣΑΓΩΓΙΚΗ Ε.Ε.</t>
   </si>
   <si>
-    <t>ΑΦΟΙ ΛΑΓΟΥ ΧΡΩΜΑΤΑ ΙΚΕ</t>
-  </si>
-  <si>
     <t>ΤΔΑ 4653</t>
   </si>
   <si>
-    <t>TΔA 60984</t>
-  </si>
-  <si>
-    <t>20-02-00-0024</t>
-  </si>
-  <si>
-    <t>54-02-02-2024</t>
+    <t>64-12-00-0087</t>
   </si>
   <si>
     <t>50-00-00-0000</t>
   </si>
   <si>
-    <t>24-02-00-0024</t>
-  </si>
-  <si>
-    <t>64-98-99-0025</t>
-  </si>
-  <si>
-    <t>63-98-08-0000</t>
-  </si>
-  <si>
     <t>Α/Α</t>
   </si>
   <si>
@@ -135,9 +111,6 @@
   </si>
   <si>
     <t>ΕΠΩΝΥΜΙΑ</t>
-  </si>
-  <si>
-    <t>800916954</t>
   </si>
   <si>
     <t>800470153</t>
@@ -505,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -612,13 +585,13 @@
         <v>142076</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I2" s="3">
         <v>24.06</v>
@@ -630,7 +603,7 @@
         <v>5.77</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
@@ -639,16 +612,16 @@
         <v>24.06</v>
       </c>
       <c r="S2" s="3">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="T2" s="3">
-        <v>24.06</v>
+        <v>29.83</v>
       </c>
       <c r="U2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="W2" s="1">
         <v>0</v>
@@ -671,13 +644,13 @@
         <v>142076</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3">
         <v>24.06</v>
@@ -689,390 +662,27 @@
         <v>5.77</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="3">
-        <v>5.77</v>
+        <v>29.83</v>
       </c>
       <c r="S3" s="3">
         <v>0</v>
       </c>
       <c r="T3" s="3">
-        <v>5.77</v>
+        <v>29.83</v>
       </c>
       <c r="U3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="W3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1">
-        <v>142076</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="3">
-        <v>24.06</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3">
-        <v>5.77</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3">
-        <v>29.83</v>
-      </c>
-      <c r="S4" s="3">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3">
-        <v>29.83</v>
-      </c>
-      <c r="U4" t="s">
-        <v>29</v>
-      </c>
-      <c r="V4" t="s">
-        <v>27</v>
-      </c>
-      <c r="W4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3">
-        <v>97.83</v>
-      </c>
-      <c r="S5" s="3">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3">
-        <v>97.83</v>
-      </c>
-      <c r="U5" t="s">
-        <v>30</v>
-      </c>
-      <c r="V5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <v>23.48</v>
-      </c>
-      <c r="S6" s="3">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
-        <v>23.48</v>
-      </c>
-      <c r="U6" t="s">
-        <v>30</v>
-      </c>
-      <c r="V6" t="s">
-        <v>28</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <v>7.16</v>
-      </c>
-      <c r="S7" s="3">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3">
-        <v>7.16</v>
-      </c>
-      <c r="U7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V7" t="s">
-        <v>28</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0.43</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0.43</v>
-      </c>
-      <c r="U8" t="s">
-        <v>30</v>
-      </c>
-      <c r="V8" t="s">
-        <v>28</v>
-      </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>14460</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3">
-        <v>104.99</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="N9" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3">
-        <v>128.9</v>
-      </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3">
-        <v>128.9</v>
-      </c>
-      <c r="U9" t="s">
-        <v>30</v>
-      </c>
-      <c r="V9" t="s">
-        <v>28</v>
-      </c>
-      <c r="W9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1083,7 +693,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -1093,35 +703,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>14460</v>
+        <v>142076</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>142076</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
